--- a/docs/content-templates/09_questions_template.xlsx
+++ b/docs/content-templates/09_questions_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
   <si>
     <t>09 — نموذج بنك الأسئلة</t>
   </si>
@@ -107,6 +107,24 @@
     <t>ملاحظة: للمحررين فقط — مثال: القوة تُقاس بالنيوتن</t>
   </si>
   <si>
+    <t>question_type</t>
+  </si>
+  <si>
+    <t>مثال: mcq</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>semester</t>
+  </si>
+  <si>
+    <t>مثال: 1</t>
+  </si>
+  <si>
+    <t>sort_order</t>
+  </si>
+  <si>
     <t>review_status</t>
   </si>
   <si>
@@ -165,6 +183,9 @@
   </si>
   <si>
     <t>القوة تُقاس بالنيوتن</t>
+  </si>
+  <si>
+    <t>mcq</t>
   </si>
   <si>
     <t>مسودة</t>
@@ -570,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -715,14 +736,25 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -730,50 +762,71 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -795,9 +848,11 @@
     <col min="11" max="11" width="21" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="14" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -837,50 +892,74 @@
       <c r="M1" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>51</v>
+        <v>57</v>
+      </c>
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
